--- a/uploads/Organograma_Rezende_v5_atualizado.xlsx
+++ b/uploads/Organograma_Rezende_v5_atualizado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rezende Energia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rezende Energia\Downloads\Gabriel\Novas implementações\organograma v6\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_327DF479A7F0323E6295E8D520302F67461CB651" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E957D7E-8AC7-450F-81A5-08ACE34CB4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="904" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="904" firstSheet="19" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Financeiro" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="264">
   <si>
     <t>id</t>
   </si>
@@ -5405,20 +5405,21 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5438,13 +5439,16 @@
         <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5463,14 +5467,17 @@
       <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>12</v>
+      <c r="G2" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5489,10 +5496,13 @@
       <c r="F3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
+      <c r="G3" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>110</v>
       </c>
     </row>

--- a/uploads/Organograma_Rezende_v5_atualizado.xlsx
+++ b/uploads/Organograma_Rezende_v5_atualizado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rezende Energia\Downloads\Gabriel\Novas implementações\organograma v6\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rezende Energia\Downloads\Gabriel\Novas implementações\Organograma v7\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E957D7E-8AC7-450F-81A5-08ACE34CB4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B583C6-7036-4B4D-BD59-0E88526B3A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="904" firstSheet="19" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="904" firstSheet="17" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Financeiro" sheetId="1" r:id="rId1"/>
@@ -318,7 +318,7 @@
     <definedName name="Z_C8CF15C5_544D_4597_938D_1CBE63AEC51A_.wvu.FilterData" hidden="1">#REF!</definedName>
     <definedName name="Z_C8CF15C5_544D_4597_938D_1CBE63AEC51A_.wvu.PrintArea" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -5412,9 +5412,9 @@
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
